--- a/database/event/6137/event_6137_evp_summary.xlsx
+++ b/database/event/6137/event_6137_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.206300000000001</v>
+        <v>9.1342</v>
       </c>
       <c r="C2" t="n">
-        <v>4.635</v>
+        <v>4.5987</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2978</v>
+        <v>3.1952</v>
       </c>
       <c r="E2" t="n">
-        <v>9.206300000000001</v>
+        <v>9.1342</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3648</v>
+        <v>5.2927</v>
       </c>
       <c r="G2" t="n">
         <v>3.8415</v>
       </c>
       <c r="H2" t="n">
-        <v>6.109</v>
+        <v>5.9959</v>
       </c>
       <c r="I2" t="n">
         <v>6.2525</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.9835</v>
+        <v>7.929</v>
       </c>
       <c r="C3" t="n">
-        <v>4.0193</v>
+        <v>3.9919</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8038</v>
+        <v>2.715</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9835</v>
+        <v>7.929</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4132</v>
+        <v>4.3587</v>
       </c>
       <c r="G3" t="n">
         <v>3.5703</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6169</v>
+        <v>4.5314</v>
       </c>
       <c r="I3" t="n">
         <v>4.7253</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.8606</v>
+        <v>7.7907</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9575</v>
+        <v>3.9223</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7541</v>
+        <v>2.6599</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8606</v>
+        <v>7.7907</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2443</v>
+        <v>5.1744</v>
       </c>
       <c r="G4" t="n">
         <v>2.6163</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9201</v>
+        <v>5.8105</v>
       </c>
       <c r="I4" t="n">
         <v>6.0591</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.8067</v>
+        <v>7.7543</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9303</v>
+        <v>3.9039</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7324</v>
+        <v>2.6454</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8067</v>
+        <v>7.7543</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9978</v>
+        <v>4.9455</v>
       </c>
       <c r="G5" t="n">
         <v>2.8088</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5336</v>
+        <v>5.4514</v>
       </c>
       <c r="I5" t="n">
         <v>5.6373</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.439</v>
+        <v>7.3826</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7452</v>
+        <v>3.7168</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5838</v>
+        <v>2.4973</v>
       </c>
       <c r="E6" t="n">
-        <v>7.439</v>
+        <v>7.3826</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5107</v>
+        <v>4.4544</v>
       </c>
       <c r="G6" t="n">
         <v>2.9283</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7697</v>
+        <v>4.6814</v>
       </c>
       <c r="I6" t="n">
         <v>4.8817</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.3209</v>
+        <v>7.2252</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6857</v>
+        <v>3.6376</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5361</v>
+        <v>2.4346</v>
       </c>
       <c r="E7" t="n">
-        <v>7.3209</v>
+        <v>7.2252</v>
       </c>
       <c r="F7" t="n">
-        <v>5.1733</v>
+        <v>5.0776</v>
       </c>
       <c r="G7" t="n">
         <v>2.1476</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8086</v>
+        <v>5.6586</v>
       </c>
       <c r="I7" t="n">
         <v>6.0006</v>
@@ -778,7 +778,7 @@
         <v>3.5093</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3945</v>
+        <v>2.3331</v>
       </c>
       <c r="E8" t="n">
         <v>6.9704</v>
@@ -790,7 +790,7 @@
         <v>0.5069</v>
       </c>
       <c r="H8" t="n">
-        <v>8.264900000000001</v>
+        <v>8.0817</v>
       </c>
       <c r="I8" t="n">
         <v>8.4985</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.9554</v>
+        <v>6.8684</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5017</v>
+        <v>3.4579</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3885</v>
+        <v>2.2925</v>
       </c>
       <c r="E9" t="n">
-        <v>6.9554</v>
+        <v>6.8684</v>
       </c>
       <c r="F9" t="n">
-        <v>4.8391</v>
+        <v>4.7521</v>
       </c>
       <c r="G9" t="n">
         <v>2.1163</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2847</v>
+        <v>5.1482</v>
       </c>
       <c r="I9" t="n">
         <v>5.4593</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.5301</v>
+        <v>6.4635</v>
       </c>
       <c r="C10" t="n">
-        <v>3.2876</v>
+        <v>3.2541</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2167</v>
+        <v>2.1311</v>
       </c>
       <c r="E10" t="n">
-        <v>6.5301</v>
+        <v>6.4635</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1713</v>
+        <v>6.4635</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3588</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1713</v>
+        <v>9.023199999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2761</v>
+        <v>9.4885</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3588</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>418</v>
+        <v>380</v>
       </c>
       <c r="L10" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>6.6349</v>
+        <v>9.4885</v>
       </c>
       <c r="N10" t="n">
-        <v>659</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.4635</v>
+        <v>6.4482</v>
       </c>
       <c r="C11" t="n">
-        <v>3.2541</v>
+        <v>3.2464</v>
       </c>
       <c r="D11" t="n">
-        <v>2.1897</v>
+        <v>2.1251</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4635</v>
+        <v>6.4482</v>
       </c>
       <c r="F11" t="n">
-        <v>6.4635</v>
+        <v>3.0894</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3.3588</v>
       </c>
       <c r="H11" t="n">
-        <v>9.2278</v>
+        <v>3.0894</v>
       </c>
       <c r="I11" t="n">
-        <v>9.4885</v>
+        <v>3.2761</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.3588</v>
       </c>
       <c r="K11" t="n">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="M11" t="n">
-        <v>9.4885</v>
+        <v>6.6349</v>
       </c>
       <c r="N11" t="n">
-        <v>380</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12">
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.2213</v>
+        <v>6.1159</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1321</v>
+        <v>3.0791</v>
       </c>
       <c r="D12" t="n">
-        <v>2.0919</v>
+        <v>1.9927</v>
       </c>
       <c r="E12" t="n">
-        <v>6.2213</v>
+        <v>6.1159</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2213</v>
+        <v>6.1159</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7.4519</v>
+        <v>7.2867</v>
       </c>
       <c r="I12" t="n">
         <v>7.6625</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.1691</v>
+        <v>6.0685</v>
       </c>
       <c r="C13" t="n">
-        <v>3.1059</v>
+        <v>3.0552</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0708</v>
+        <v>1.9738</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1691</v>
+        <v>6.0685</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0041</v>
+        <v>5.9035</v>
       </c>
       <c r="G13" t="n">
         <v>0.165</v>
       </c>
       <c r="H13" t="n">
-        <v>7.1113</v>
+        <v>6.9536</v>
       </c>
       <c r="I13" t="n">
         <v>7.3122</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8658</v>
+        <v>5.8069</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9532</v>
+        <v>2.9235</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9483</v>
+        <v>1.8696</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8658</v>
+        <v>5.8069</v>
       </c>
       <c r="F14" t="n">
-        <v>4.65</v>
+        <v>4.5911</v>
       </c>
       <c r="G14" t="n">
         <v>1.2158</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9882</v>
+        <v>4.8958</v>
       </c>
       <c r="I14" t="n">
         <v>5.1053</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7775</v>
+        <v>5.7279</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9087</v>
+        <v>2.8837</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9126</v>
+        <v>1.8381</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7775</v>
+        <v>5.7279</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1495</v>
+        <v>4.0999</v>
       </c>
       <c r="G15" t="n">
         <v>1.628</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2034</v>
+        <v>4.1256</v>
       </c>
       <c r="I15" t="n">
         <v>4.3022</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6528</v>
+        <v>5.6216</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8459</v>
+        <v>2.8302</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8622</v>
+        <v>1.7957</v>
       </c>
       <c r="E16" t="n">
-        <v>5.6528</v>
+        <v>5.6216</v>
       </c>
       <c r="F16" t="n">
-        <v>5.6528</v>
+        <v>5.6216</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>6.5604</v>
+        <v>6.5116</v>
       </c>
       <c r="I16" t="n">
         <v>6.6217</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6449</v>
+        <v>5.5752</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8419</v>
+        <v>2.8069</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8591</v>
+        <v>1.7772</v>
       </c>
       <c r="E17" t="n">
-        <v>5.6449</v>
+        <v>5.5752</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7635</v>
+        <v>3.6938</v>
       </c>
       <c r="G17" t="n">
         <v>1.8814</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7635</v>
+        <v>3.6938</v>
       </c>
       <c r="I17" t="n">
         <v>3.8519</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.3938</v>
+        <v>5.3645</v>
       </c>
       <c r="C18" t="n">
-        <v>2.7155</v>
+        <v>2.7008</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7576</v>
+        <v>1.6933</v>
       </c>
       <c r="E18" t="n">
-        <v>5.3938</v>
+        <v>5.3645</v>
       </c>
       <c r="F18" t="n">
-        <v>5.3938</v>
+        <v>5.3645</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>6.1543</v>
+        <v>6.1085</v>
       </c>
       <c r="I18" t="n">
         <v>6.2118</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.3445</v>
+        <v>5.2585</v>
       </c>
       <c r="C19" t="n">
-        <v>2.6907</v>
+        <v>2.6474</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7377</v>
+        <v>1.6511</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3445</v>
+        <v>5.2585</v>
       </c>
       <c r="F19" t="n">
-        <v>5.3445</v>
+        <v>5.2585</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>6.0771</v>
+        <v>5.9423</v>
       </c>
       <c r="I19" t="n">
         <v>6.2488</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.1942</v>
+        <v>5.1437</v>
       </c>
       <c r="C20" t="n">
-        <v>2.615</v>
+        <v>2.5896</v>
       </c>
       <c r="D20" t="n">
-        <v>1.677</v>
+        <v>1.6053</v>
       </c>
       <c r="E20" t="n">
-        <v>5.1942</v>
+        <v>5.1437</v>
       </c>
       <c r="F20" t="n">
-        <v>4.1962</v>
+        <v>4.1457</v>
       </c>
       <c r="G20" t="n">
         <v>0.998</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2766</v>
+        <v>4.1974</v>
       </c>
       <c r="I20" t="n">
         <v>4.377</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.1123</v>
+        <v>5.0274</v>
       </c>
       <c r="C21" t="n">
-        <v>2.5738</v>
+        <v>2.5311</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6439</v>
+        <v>1.559</v>
       </c>
       <c r="E21" t="n">
-        <v>5.1123</v>
+        <v>5.0274</v>
       </c>
       <c r="F21" t="n">
-        <v>5.2971</v>
+        <v>5.2122</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1848</v>
       </c>
       <c r="H21" t="n">
-        <v>6.0028</v>
+        <v>5.8697</v>
       </c>
       <c r="I21" t="n">
         <v>6.1724</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.0155</v>
+        <v>4.9263</v>
       </c>
       <c r="C22" t="n">
-        <v>2.5251</v>
+        <v>2.4802</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6048</v>
+        <v>1.5187</v>
       </c>
       <c r="E22" t="n">
-        <v>5.0155</v>
+        <v>4.9263</v>
       </c>
       <c r="F22" t="n">
-        <v>5.4905</v>
+        <v>5.4013</v>
       </c>
       <c r="G22" t="n">
         <v>-0.475</v>
       </c>
       <c r="H22" t="n">
-        <v>6.3061</v>
+        <v>6.1662</v>
       </c>
       <c r="I22" t="n">
         <v>6.4842</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.9375</v>
+        <v>4.8651</v>
       </c>
       <c r="C23" t="n">
-        <v>2.4858</v>
+        <v>2.4494</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5733</v>
+        <v>1.4943</v>
       </c>
       <c r="E23" t="n">
-        <v>4.9375</v>
+        <v>4.8651</v>
       </c>
       <c r="F23" t="n">
-        <v>4.7349</v>
+        <v>4.6625</v>
       </c>
       <c r="G23" t="n">
         <v>0.2026</v>
       </c>
       <c r="H23" t="n">
-        <v>5.1213</v>
+        <v>5.0077</v>
       </c>
       <c r="I23" t="n">
         <v>5.266</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.7178</v>
+        <v>4.6434</v>
       </c>
       <c r="C24" t="n">
-        <v>2.3752</v>
+        <v>2.3377</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4845</v>
+        <v>1.406</v>
       </c>
       <c r="E24" t="n">
-        <v>4.7178</v>
+        <v>4.6434</v>
       </c>
       <c r="F24" t="n">
-        <v>5.4902</v>
+        <v>5.4158</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7724</v>
       </c>
       <c r="H24" t="n">
-        <v>6.3056</v>
+        <v>6.1889</v>
       </c>
       <c r="I24" t="n">
         <v>6.4537</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.6342</v>
+        <v>4.5873</v>
       </c>
       <c r="C25" t="n">
-        <v>2.3331</v>
+        <v>2.3095</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4508</v>
+        <v>1.3837</v>
       </c>
       <c r="E25" t="n">
-        <v>4.6342</v>
+        <v>4.5873</v>
       </c>
       <c r="F25" t="n">
-        <v>4.6342</v>
+        <v>4.5873</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9634</v>
+        <v>4.8898</v>
       </c>
       <c r="I25" t="n">
         <v>5.0565</v>
@@ -1606,7 +1606,7 @@
         <v>2.3004</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4245</v>
+        <v>1.3765</v>
       </c>
       <c r="E26" t="n">
         <v>4.5693</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.4762</v>
+        <v>4.4466</v>
       </c>
       <c r="C27" t="n">
-        <v>2.2536</v>
+        <v>2.2387</v>
       </c>
       <c r="D27" t="n">
-        <v>1.3869</v>
+        <v>1.3276</v>
       </c>
       <c r="E27" t="n">
-        <v>4.4762</v>
+        <v>4.4466</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5993</v>
+        <v>1.5697</v>
       </c>
       <c r="G27" t="n">
         <v>2.8769</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5993</v>
+        <v>1.5697</v>
       </c>
       <c r="I27" t="n">
         <v>1.6369</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.3391</v>
+        <v>4.2943</v>
       </c>
       <c r="C28" t="n">
-        <v>2.1845</v>
+        <v>2.162</v>
       </c>
       <c r="D28" t="n">
-        <v>1.3315</v>
+        <v>1.2669</v>
       </c>
       <c r="E28" t="n">
-        <v>4.3391</v>
+        <v>4.2943</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7323</v>
+        <v>1.6875</v>
       </c>
       <c r="G28" t="n">
         <v>2.6068</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7323</v>
+        <v>1.6875</v>
       </c>
       <c r="I28" t="n">
         <v>1.7895</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.2877</v>
+        <v>4.2523</v>
       </c>
       <c r="C29" t="n">
-        <v>2.1587</v>
+        <v>2.1408</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3108</v>
+        <v>1.2502</v>
       </c>
       <c r="E29" t="n">
-        <v>4.2877</v>
+        <v>4.2523</v>
       </c>
       <c r="F29" t="n">
-        <v>4.7163</v>
+        <v>4.2523</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4286</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5.0921</v>
+        <v>4.3646</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2359</v>
+        <v>4.3646</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4286</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="L29" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.8073</v>
+        <v>4.3646</v>
       </c>
       <c r="N29" t="n">
-        <v>464</v>
+        <v>360</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.2523</v>
+        <v>4.2157</v>
       </c>
       <c r="C30" t="n">
-        <v>2.1408</v>
+        <v>2.1224</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2965</v>
+        <v>1.2356</v>
       </c>
       <c r="E30" t="n">
-        <v>4.2523</v>
+        <v>4.2157</v>
       </c>
       <c r="F30" t="n">
-        <v>4.2523</v>
+        <v>4.6443</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4286</v>
       </c>
       <c r="H30" t="n">
-        <v>4.3646</v>
+        <v>4.9791</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3646</v>
+        <v>5.2359</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4286</v>
       </c>
       <c r="K30" t="n">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3646</v>
+        <v>4.8073</v>
       </c>
       <c r="N30" t="n">
-        <v>360</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31">
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.2129</v>
+        <v>4.1562</v>
       </c>
       <c r="C31" t="n">
-        <v>2.121</v>
+        <v>2.0925</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2806</v>
+        <v>1.2119</v>
       </c>
       <c r="E31" t="n">
-        <v>4.2129</v>
+        <v>4.1562</v>
       </c>
       <c r="F31" t="n">
-        <v>3.821</v>
+        <v>3.7643</v>
       </c>
       <c r="G31" t="n">
         <v>0.3919</v>
       </c>
       <c r="H31" t="n">
-        <v>3.821</v>
+        <v>3.7643</v>
       </c>
       <c r="I31" t="n">
         <v>3.8926</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.2056</v>
+        <v>4.1201</v>
       </c>
       <c r="C32" t="n">
-        <v>2.1173</v>
+        <v>2.0743</v>
       </c>
       <c r="D32" t="n">
-        <v>1.2776</v>
+        <v>1.1975</v>
       </c>
       <c r="E32" t="n">
-        <v>4.2056</v>
+        <v>4.1201</v>
       </c>
       <c r="F32" t="n">
-        <v>3.8856</v>
+        <v>4.1201</v>
       </c>
       <c r="G32" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.8856</v>
+        <v>4.1573</v>
       </c>
       <c r="I32" t="n">
-        <v>3.9954</v>
+        <v>4.3353</v>
       </c>
       <c r="J32" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3154</v>
+        <v>4.3353</v>
       </c>
       <c r="N32" t="n">
-        <v>464</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.1702</v>
+        <v>4.1194</v>
       </c>
       <c r="C33" t="n">
-        <v>2.0995</v>
+        <v>2.0739</v>
       </c>
       <c r="D33" t="n">
-        <v>1.2633</v>
+        <v>1.1973</v>
       </c>
       <c r="E33" t="n">
-        <v>4.1702</v>
+        <v>4.1194</v>
       </c>
       <c r="F33" t="n">
-        <v>4.1702</v>
+        <v>3.7994</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="H33" t="n">
-        <v>4.2358</v>
+        <v>3.7994</v>
       </c>
       <c r="I33" t="n">
-        <v>4.3353</v>
+        <v>3.9954</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="K33" t="n">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3353</v>
+        <v>4.3154</v>
       </c>
       <c r="N33" t="n">
-        <v>410</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34">
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.0726</v>
+        <v>4.0524</v>
       </c>
       <c r="C34" t="n">
-        <v>2.0504</v>
+        <v>2.0402</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2239</v>
+        <v>1.1706</v>
       </c>
       <c r="E34" t="n">
-        <v>4.0726</v>
+        <v>4.0524</v>
       </c>
       <c r="F34" t="n">
-        <v>4.0726</v>
+        <v>4.0524</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4.0828</v>
+        <v>4.0524</v>
       </c>
       <c r="I34" t="n">
         <v>4.1209</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.8431</v>
+        <v>3.8144</v>
       </c>
       <c r="C35" t="n">
-        <v>1.9348</v>
+        <v>1.9204</v>
       </c>
       <c r="D35" t="n">
-        <v>1.1312</v>
+        <v>1.0757</v>
       </c>
       <c r="E35" t="n">
-        <v>3.8431</v>
+        <v>3.8144</v>
       </c>
       <c r="F35" t="n">
-        <v>3.8431</v>
+        <v>3.8144</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.8431</v>
+        <v>3.8144</v>
       </c>
       <c r="I35" t="n">
         <v>3.8789</v>
@@ -2066,7 +2066,7 @@
         <v>1.7532</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9434</v>
       </c>
       <c r="E36" t="n">
         <v>3.4823</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.2192</v>
+        <v>3.2072</v>
       </c>
       <c r="C37" t="n">
-        <v>1.6207</v>
+        <v>1.6147</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8791</v>
+        <v>0.8338</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2192</v>
+        <v>3.2072</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2192</v>
+        <v>3.2072</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2192</v>
+        <v>3.2072</v>
       </c>
       <c r="I37" t="n">
         <v>3.2342</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.189</v>
+        <v>3.1771</v>
       </c>
       <c r="C38" t="n">
-        <v>1.6055</v>
+        <v>1.5995</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8669</v>
+        <v>0.8218</v>
       </c>
       <c r="E38" t="n">
-        <v>3.189</v>
+        <v>3.1771</v>
       </c>
       <c r="F38" t="n">
-        <v>3.189</v>
+        <v>3.1771</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.189</v>
+        <v>3.1771</v>
       </c>
       <c r="I38" t="n">
         <v>3.2038</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.1806</v>
+        <v>3.1688</v>
       </c>
       <c r="C39" t="n">
-        <v>1.6013</v>
+        <v>1.5953</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8635</v>
+        <v>0.8185</v>
       </c>
       <c r="E39" t="n">
-        <v>3.1806</v>
+        <v>3.1688</v>
       </c>
       <c r="F39" t="n">
-        <v>3.1806</v>
+        <v>3.1688</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1806</v>
+        <v>3.1688</v>
       </c>
       <c r="I39" t="n">
         <v>3.1955</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.1409</v>
+        <v>3.0894</v>
       </c>
       <c r="C40" t="n">
-        <v>1.5813</v>
+        <v>1.5554</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8475</v>
+        <v>0.7869</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1409</v>
+        <v>3.0894</v>
       </c>
       <c r="F40" t="n">
-        <v>3.4677</v>
+        <v>3.4162</v>
       </c>
       <c r="G40" t="n">
         <v>-0.3268</v>
       </c>
       <c r="H40" t="n">
-        <v>3.4677</v>
+        <v>3.4162</v>
       </c>
       <c r="I40" t="n">
         <v>3.5327</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.0573</v>
+        <v>3.0119</v>
       </c>
       <c r="C41" t="n">
-        <v>1.5392</v>
+        <v>1.5164</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8137</v>
+        <v>0.756</v>
       </c>
       <c r="E41" t="n">
-        <v>3.0573</v>
+        <v>3.0119</v>
       </c>
       <c r="F41" t="n">
-        <v>3.0573</v>
+        <v>3.0119</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3.0573</v>
+        <v>3.0119</v>
       </c>
       <c r="I41" t="n">
         <v>3.1146</v>
@@ -2342,7 +2342,7 @@
         <v>1.4695</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7578</v>
+        <v>0.7189</v>
       </c>
       <c r="E42" t="n">
         <v>2.9188</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.8887</v>
+        <v>2.8672</v>
       </c>
       <c r="C43" t="n">
-        <v>1.4543</v>
+        <v>1.4435</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7456</v>
+        <v>0.6984</v>
       </c>
       <c r="E43" t="n">
-        <v>2.8887</v>
+        <v>2.8672</v>
       </c>
       <c r="F43" t="n">
-        <v>2.8887</v>
+        <v>2.8672</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.8887</v>
+        <v>2.8672</v>
       </c>
       <c r="I43" t="n">
         <v>2.9157</v>
@@ -2424,93 +2424,93 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Krad</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.8654</v>
+        <v>2.8006</v>
       </c>
       <c r="C44" t="n">
-        <v>1.4426</v>
+        <v>1.41</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7362</v>
+        <v>0.6718</v>
       </c>
       <c r="E44" t="n">
-        <v>2.8654</v>
+        <v>2.8006</v>
       </c>
       <c r="F44" t="n">
-        <v>3.6418</v>
+        <v>2.8006</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.7764</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.6418</v>
+        <v>2.8006</v>
       </c>
       <c r="I44" t="n">
-        <v>3.7447</v>
+        <v>2.9205</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.7764</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>314</v>
+        <v>410</v>
       </c>
       <c r="L44" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.9683</v>
+        <v>2.9205</v>
       </c>
       <c r="N44" t="n">
-        <v>369</v>
+        <v>410</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Krad</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.8535</v>
+        <v>2.7846</v>
       </c>
       <c r="C45" t="n">
-        <v>1.4366</v>
+        <v>1.4019</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.6655</v>
       </c>
       <c r="E45" t="n">
-        <v>2.8535</v>
+        <v>2.7846</v>
       </c>
       <c r="F45" t="n">
-        <v>2.8535</v>
+        <v>3.561</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.7764</v>
       </c>
       <c r="H45" t="n">
-        <v>2.8535</v>
+        <v>3.561</v>
       </c>
       <c r="I45" t="n">
-        <v>2.9205</v>
+        <v>3.7447</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.7764</v>
       </c>
       <c r="K45" t="n">
-        <v>410</v>
+        <v>314</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.9205</v>
+        <v>2.9683</v>
       </c>
       <c r="N45" t="n">
-        <v>410</v>
+        <v>369</v>
       </c>
     </row>
     <row r="46">
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.5218</v>
+        <v>2.5124</v>
       </c>
       <c r="C46" t="n">
-        <v>1.2696</v>
+        <v>1.2649</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5974</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>2.5218</v>
+        <v>2.5124</v>
       </c>
       <c r="F46" t="n">
-        <v>2.5218</v>
+        <v>2.5124</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5218</v>
+        <v>2.5124</v>
       </c>
       <c r="I46" t="n">
         <v>2.5336</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.3746</v>
+        <v>2.3658</v>
       </c>
       <c r="C47" t="n">
-        <v>1.1955</v>
+        <v>1.1911</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5379</v>
+        <v>0.4986</v>
       </c>
       <c r="E47" t="n">
-        <v>2.3746</v>
+        <v>2.3658</v>
       </c>
       <c r="F47" t="n">
-        <v>2.3746</v>
+        <v>2.3658</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.3746</v>
+        <v>2.3658</v>
       </c>
       <c r="I47" t="n">
         <v>2.3857</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.3481</v>
+        <v>2.3132</v>
       </c>
       <c r="C48" t="n">
-        <v>1.1822</v>
+        <v>1.1646</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5272</v>
+        <v>0.4777</v>
       </c>
       <c r="E48" t="n">
-        <v>2.3481</v>
+        <v>2.3132</v>
       </c>
       <c r="F48" t="n">
-        <v>2.3481</v>
+        <v>2.3132</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.3481</v>
+        <v>2.3132</v>
       </c>
       <c r="I48" t="n">
         <v>2.3921</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.2729</v>
+        <v>2.2472</v>
       </c>
       <c r="C49" t="n">
-        <v>1.1443</v>
+        <v>1.1314</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4968</v>
+        <v>0.4514</v>
       </c>
       <c r="E49" t="n">
-        <v>2.2729</v>
+        <v>2.2472</v>
       </c>
       <c r="F49" t="n">
-        <v>1.7318</v>
+        <v>1.7061</v>
       </c>
       <c r="G49" t="n">
         <v>0.5411</v>
       </c>
       <c r="H49" t="n">
-        <v>1.7318</v>
+        <v>1.7061</v>
       </c>
       <c r="I49" t="n">
         <v>1.7643</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.2459</v>
+        <v>2.2292</v>
       </c>
       <c r="C50" t="n">
-        <v>1.1307</v>
+        <v>1.1223</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4859</v>
+        <v>0.4442</v>
       </c>
       <c r="E50" t="n">
-        <v>2.2459</v>
+        <v>2.2292</v>
       </c>
       <c r="F50" t="n">
-        <v>2.2459</v>
+        <v>2.2292</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2.2459</v>
+        <v>2.2292</v>
       </c>
       <c r="I50" t="n">
         <v>2.2668</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.1886</v>
+        <v>2.1723</v>
       </c>
       <c r="C51" t="n">
-        <v>1.1019</v>
+        <v>1.0937</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4628</v>
+        <v>0.4215</v>
       </c>
       <c r="E51" t="n">
-        <v>2.1886</v>
+        <v>2.1723</v>
       </c>
       <c r="F51" t="n">
-        <v>2.1886</v>
+        <v>2.1723</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.1886</v>
+        <v>2.1723</v>
       </c>
       <c r="I51" t="n">
         <v>2.209</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.0586</v>
+        <v>2.0281</v>
       </c>
       <c r="C52" t="n">
-        <v>1.0364</v>
+        <v>1.0211</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4103</v>
+        <v>0.3641</v>
       </c>
       <c r="E52" t="n">
-        <v>2.0586</v>
+        <v>2.0281</v>
       </c>
       <c r="F52" t="n">
-        <v>2.0586</v>
+        <v>2.0281</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.0586</v>
+        <v>2.0281</v>
       </c>
       <c r="I52" t="n">
         <v>2.0972</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.8362</v>
+        <v>1.7955</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9244</v>
+        <v>0.904</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3204</v>
+        <v>0.2714</v>
       </c>
       <c r="E53" t="n">
-        <v>1.8362</v>
+        <v>1.7955</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8362</v>
+        <v>1.7955</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8362</v>
+        <v>1.7955</v>
       </c>
       <c r="I53" t="n">
         <v>1.8881</v>
@@ -2884,93 +2884,93 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.7512</v>
+        <v>1.7009</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8563</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2861</v>
+        <v>0.2337</v>
       </c>
       <c r="E54" t="n">
-        <v>1.7512</v>
+        <v>1.7009</v>
       </c>
       <c r="F54" t="n">
-        <v>2.7512</v>
+        <v>0.1224</v>
       </c>
       <c r="G54" t="n">
-        <v>-1</v>
+        <v>1.5785</v>
       </c>
       <c r="H54" t="n">
-        <v>2.7512</v>
+        <v>0.1224</v>
       </c>
       <c r="I54" t="n">
-        <v>2.829</v>
+        <v>0.1298</v>
       </c>
       <c r="J54" t="n">
-        <v>-1</v>
+        <v>1.5785</v>
       </c>
       <c r="K54" t="n">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="L54" t="n">
-        <v>69</v>
+        <v>241</v>
       </c>
       <c r="M54" t="n">
-        <v>1.829</v>
+        <v>1.7083</v>
       </c>
       <c r="N54" t="n">
-        <v>464</v>
+        <v>659</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.7042</v>
+        <v>1.6902</v>
       </c>
       <c r="C55" t="n">
-        <v>0.858</v>
+        <v>0.8509</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2671</v>
+        <v>0.2295</v>
       </c>
       <c r="E55" t="n">
-        <v>1.7042</v>
+        <v>1.6902</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1256</v>
+        <v>2.6902</v>
       </c>
       <c r="G55" t="n">
-        <v>1.5785</v>
+        <v>-1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1256</v>
+        <v>2.6902</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1298</v>
+        <v>2.829</v>
       </c>
       <c r="J55" t="n">
-        <v>1.5785</v>
+        <v>-1</v>
       </c>
       <c r="K55" t="n">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="L55" t="n">
-        <v>241</v>
+        <v>69</v>
       </c>
       <c r="M55" t="n">
-        <v>1.7083</v>
+        <v>1.829</v>
       </c>
       <c r="N55" t="n">
-        <v>659</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56">
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.6979</v>
+        <v>1.6665</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8548</v>
+        <v>0.839</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2646</v>
+        <v>0.22</v>
       </c>
       <c r="E56" t="n">
-        <v>1.6979</v>
+        <v>1.6665</v>
       </c>
       <c r="F56" t="n">
-        <v>1.6979</v>
+        <v>1.6665</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.6979</v>
+        <v>1.6665</v>
       </c>
       <c r="I56" t="n">
         <v>1.7378</v>
@@ -3032,7 +3032,7 @@
         <v>0.8001</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2207</v>
+        <v>0.1893</v>
       </c>
       <c r="E57" t="n">
         <v>1.5893</v>
@@ -3078,7 +3078,7 @@
         <v>0.59</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0521</v>
+        <v>0.023</v>
       </c>
       <c r="E58" t="n">
         <v>1.1719</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9343</v>
+        <v>0.9273</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4704</v>
+        <v>0.4669</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.0439</v>
+        <v>-0.0745</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9343</v>
+        <v>0.9273</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9343</v>
+        <v>0.9273</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9343</v>
+        <v>0.9273</v>
       </c>
       <c r="I59" t="n">
         <v>0.9429999999999999</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9132</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4598</v>
+        <v>0.458</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.0524</v>
+        <v>-0.0814</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9132</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9132</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9132</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>0.9175</v>
@@ -3216,7 +3216,7 @@
         <v>0.4534</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.0575</v>
+        <v>-0.0851</v>
       </c>
       <c r="E61" t="n">
         <v>0.9006</v>
@@ -3262,7 +3262,7 @@
         <v>0.3315</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.1553</v>
+        <v>-0.1816</v>
       </c>
       <c r="E62" t="n">
         <v>0.6585</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6081</v>
+        <v>0.6036</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3062</v>
+        <v>0.3039</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.1757</v>
+        <v>-0.2034</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6081</v>
+        <v>0.6036</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6081</v>
+        <v>0.6036</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6081</v>
+        <v>0.6036</v>
       </c>
       <c r="I63" t="n">
         <v>0.6138</v>
@@ -3354,7 +3354,7 @@
         <v>0.2712</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.2037</v>
+        <v>-0.2293</v>
       </c>
       <c r="E64" t="n">
         <v>0.5387</v>
@@ -3400,7 +3400,7 @@
         <v>0.2473</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.2229</v>
+        <v>-0.2482</v>
       </c>
       <c r="E65" t="n">
         <v>0.4913</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4648</v>
+        <v>0.4408</v>
       </c>
       <c r="C66" t="n">
-        <v>0.234</v>
+        <v>0.2219</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.2336</v>
+        <v>-0.2683</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4648</v>
+        <v>0.4408</v>
       </c>
       <c r="F66" t="n">
-        <v>1.0834</v>
+        <v>1.0594</v>
       </c>
       <c r="G66" t="n">
         <v>-0.6186</v>
       </c>
       <c r="H66" t="n">
-        <v>1.0834</v>
+        <v>1.0594</v>
       </c>
       <c r="I66" t="n">
         <v>1.114</v>
@@ -3482,35 +3482,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4237</v>
+        <v>0.4117</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2133</v>
+        <v>0.2073</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.2502</v>
+        <v>-0.2799</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4237</v>
+        <v>0.4117</v>
       </c>
       <c r="F67" t="n">
-        <v>1.7342</v>
+        <v>0.1554</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.3105</v>
+        <v>0.2563</v>
       </c>
       <c r="H67" t="n">
-        <v>1.7342</v>
+        <v>0.1554</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7749</v>
+        <v>0.162</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.3105</v>
+        <v>0.2563</v>
       </c>
       <c r="K67" t="n">
         <v>369</v>
@@ -3519,7 +3519,7 @@
         <v>140</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4643999999999999</v>
+        <v>0.4183</v>
       </c>
       <c r="N67" t="n">
         <v>509</v>
@@ -3528,93 +3528,93 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4173</v>
+        <v>0.3916</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2101</v>
+        <v>0.1972</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2528</v>
+        <v>-0.2879</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4173</v>
+        <v>0.3916</v>
       </c>
       <c r="F68" t="n">
-        <v>1.8109</v>
+        <v>1.7021</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.3936</v>
+        <v>-1.3105</v>
       </c>
       <c r="H68" t="n">
-        <v>1.8109</v>
+        <v>1.7021</v>
       </c>
       <c r="I68" t="n">
-        <v>1.8449</v>
+        <v>1.7749</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.3936</v>
+        <v>-1.3105</v>
       </c>
       <c r="K68" t="n">
-        <v>299</v>
+        <v>369</v>
       </c>
       <c r="L68" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M68" t="n">
-        <v>0.4513</v>
+        <v>0.4643999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>443</v>
+        <v>509</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4146</v>
+        <v>0.3905</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2087</v>
+        <v>0.1966</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.2539</v>
+        <v>-0.2883</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4146</v>
+        <v>0.3905</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1583</v>
+        <v>1.7841</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2563</v>
+        <v>-1.3936</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1583</v>
+        <v>1.7841</v>
       </c>
       <c r="I69" t="n">
-        <v>0.162</v>
+        <v>1.8449</v>
       </c>
       <c r="J69" t="n">
-        <v>0.2563</v>
+        <v>-1.3936</v>
       </c>
       <c r="K69" t="n">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="L69" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M69" t="n">
-        <v>0.4183</v>
+        <v>0.4513</v>
       </c>
       <c r="N69" t="n">
-        <v>509</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70">
@@ -3630,7 +3630,7 @@
         <v>0.1745</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.2813</v>
+        <v>-0.3058</v>
       </c>
       <c r="E70" t="n">
         <v>0.3467</v>
@@ -3676,7 +3676,7 @@
         <v>0.1568</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2956</v>
+        <v>-0.3198</v>
       </c>
       <c r="E71" t="n">
         <v>0.3114</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2844</v>
+        <v>0.2823</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1432</v>
+        <v>0.1421</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.3065</v>
+        <v>-0.3314</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2844</v>
+        <v>0.2823</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2844</v>
+        <v>0.2823</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2844</v>
+        <v>0.2823</v>
       </c>
       <c r="I72" t="n">
         <v>0.2871</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.2144</v>
+        <v>0.1928</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1079</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.3347</v>
+        <v>-0.3671</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2144</v>
+        <v>0.1928</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9735</v>
+        <v>0.9519</v>
       </c>
       <c r="G73" t="n">
         <v>-0.7591</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9735</v>
+        <v>0.9519</v>
       </c>
       <c r="I73" t="n">
         <v>1.001</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.196</v>
+        <v>0.1724</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0987</v>
+        <v>0.0868</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.3422</v>
+        <v>-0.3752</v>
       </c>
       <c r="E74" t="n">
-        <v>0.196</v>
+        <v>0.1724</v>
       </c>
       <c r="F74" t="n">
-        <v>1.0652</v>
+        <v>1.0416</v>
       </c>
       <c r="G74" t="n">
         <v>-0.8692</v>
       </c>
       <c r="H74" t="n">
-        <v>1.0652</v>
+        <v>1.0416</v>
       </c>
       <c r="I74" t="n">
         <v>1.0953</v>
@@ -3860,7 +3860,7 @@
         <v>0.0813</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.3561</v>
+        <v>-0.3796</v>
       </c>
       <c r="E75" t="n">
         <v>0.1615</v>
@@ -3906,7 +3906,7 @@
         <v>0.058</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.3748</v>
+        <v>-0.398</v>
       </c>
       <c r="E76" t="n">
         <v>0.1152</v>
@@ -3952,7 +3952,7 @@
         <v>0.0521</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.3796</v>
+        <v>-0.4027</v>
       </c>
       <c r="E77" t="n">
         <v>0.1035</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0108</v>
+        <v>0.0107</v>
       </c>
       <c r="C78" t="n">
         <v>0.0054</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.417</v>
+        <v>-0.4396</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0108</v>
+        <v>0.0107</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0108</v>
+        <v>0.0107</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0108</v>
+        <v>0.0107</v>
       </c>
       <c r="I78" t="n">
         <v>0.0109</v>
@@ -4044,7 +4044,7 @@
         <v>-0.0304</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.4457</v>
+        <v>-0.4679</v>
       </c>
       <c r="E79" t="n">
         <v>-0.0603</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.2882</v>
+        <v>-0.2828</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1451</v>
+        <v>-0.1424</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5566</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.2882</v>
+        <v>-0.2828</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.2882</v>
+        <v>-0.2828</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.2882</v>
+        <v>-0.2828</v>
       </c>
       <c r="I80" t="n">
         <v>-0.2949</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.4021</v>
+        <v>-0.4006</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.2024</v>
+        <v>-0.2017</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.5838</v>
+        <v>-0.6035</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.4021</v>
+        <v>-0.4006</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.4021</v>
+        <v>-0.4006</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.4021</v>
+        <v>-0.4006</v>
       </c>
       <c r="I81" t="n">
         <v>-0.404</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.4777</v>
+        <v>-0.4873</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.2405</v>
+        <v>-0.2453</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.6143</v>
+        <v>-0.6381</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.4777</v>
+        <v>-0.4873</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4349</v>
+        <v>0.4253</v>
       </c>
       <c r="G82" t="n">
         <v>-0.9126</v>
       </c>
       <c r="H82" t="n">
-        <v>0.4349</v>
+        <v>0.4253</v>
       </c>
       <c r="I82" t="n">
         <v>0.4472</v>
@@ -4228,7 +4228,7 @@
         <v>-0.2631</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.6324</v>
+        <v>-0.6521</v>
       </c>
       <c r="E83" t="n">
         <v>-0.5225</v>
@@ -4268,25 +4268,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5435</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.2748</v>
+        <v>-0.2736</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.6419</v>
+        <v>-0.6604</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5435</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.1333</v>
+        <v>-0.1309</v>
       </c>
       <c r="G84" t="n">
         <v>-0.4126</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.1333</v>
+        <v>-0.1309</v>
       </c>
       <c r="I84" t="n">
         <v>-0.1365</v>
@@ -4314,25 +4314,25 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6339</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.3191</v>
+        <v>-0.3144</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.6774</v>
+        <v>-0.6927</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.6339</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.6339</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.6339</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="I85" t="n">
         <v>-0.6458</v>
@@ -4366,7 +4366,7 @@
         <v>-0.3237</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.6811</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="E86" t="n">
         <v>-0.643</v>
@@ -4412,7 +4412,7 @@
         <v>-0.3614</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.7113</v>
+        <v>-0.7299</v>
       </c>
       <c r="E87" t="n">
         <v>-0.7178</v>
@@ -4458,7 +4458,7 @@
         <v>-0.3646</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.7139</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="E88" t="n">
         <v>-0.7241</v>
@@ -4504,7 +4504,7 @@
         <v>-0.3678</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.7165</v>
+        <v>-0.735</v>
       </c>
       <c r="E89" t="n">
         <v>-0.7306</v>
@@ -4544,25 +4544,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.7309</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.3707</v>
+        <v>-0.368</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.7189</v>
+        <v>-0.7351</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.7309</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.7309</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.7309</v>
       </c>
       <c r="I90" t="n">
         <v>-0.7433</v>
@@ -4596,7 +4596,7 @@
         <v>-0.4134</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.7531</v>
+        <v>-0.771</v>
       </c>
       <c r="E91" t="n">
         <v>-0.8211000000000001</v>
@@ -4636,25 +4636,25 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.8511</v>
+        <v>-0.8354</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.4285</v>
+        <v>-0.4206</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.7652</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.8511</v>
+        <v>-0.8354</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.8511</v>
+        <v>-0.8354</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.8511</v>
+        <v>-0.8354</v>
       </c>
       <c r="I92" t="n">
         <v>-0.8711</v>
@@ -4688,7 +4688,7 @@
         <v>-0.44</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.7744</v>
+        <v>-0.7921</v>
       </c>
       <c r="E93" t="n">
         <v>-0.874</v>
@@ -4724,93 +4724,93 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>Peppzor</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.9008</v>
+        <v>-0.8959</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.4535</v>
+        <v>-0.451</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.7853</v>
+        <v>-0.8008</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.9008</v>
+        <v>-0.8959</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.9008</v>
+        <v>-0.8959</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.9008</v>
+        <v>-0.8959</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.905</v>
+        <v>-0.911</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>290</v>
+        <v>372</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>-0.905</v>
+        <v>-0.911</v>
       </c>
       <c r="N94" t="n">
-        <v>290</v>
+        <v>372</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Peppzor</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.9026</v>
+        <v>-0.8974</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.4544</v>
+        <v>-0.4518</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.786</v>
+        <v>-0.8014</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.9026</v>
+        <v>-0.8974</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.9026</v>
+        <v>-0.8974</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.9026</v>
+        <v>-0.8974</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.911</v>
+        <v>-0.905</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>372</v>
+        <v>290</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.911</v>
+        <v>-0.905</v>
       </c>
       <c r="N95" t="n">
-        <v>372</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96">
@@ -4826,7 +4826,7 @@
         <v>-0.5196</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.8383</v>
+        <v>-0.8551</v>
       </c>
       <c r="E96" t="n">
         <v>-1.032</v>
@@ -4866,25 +4866,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-1.0965</v>
+        <v>-1.0916</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.552</v>
+        <v>-0.5496</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.8643</v>
+        <v>-0.8788</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.0965</v>
+        <v>-1.0916</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.2631</v>
+        <v>-0.2582</v>
       </c>
       <c r="G97" t="n">
         <v>-0.8334</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.2631</v>
+        <v>-0.2582</v>
       </c>
       <c r="I97" t="n">
         <v>-0.2693</v>
@@ -4918,7 +4918,7 @@
         <v>-0.5665</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.876</v>
+        <v>-0.8922</v>
       </c>
       <c r="E98" t="n">
         <v>-1.1253</v>
@@ -4958,25 +4958,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.1588</v>
+        <v>-1.1502</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.5834</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.8895</v>
+        <v>-0.9022</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.1588</v>
+        <v>-1.1502</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.1588</v>
+        <v>-1.1502</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.1588</v>
+        <v>-1.1502</v>
       </c>
       <c r="I99" t="n">
         <v>-1.1696</v>
@@ -5010,7 +5010,7 @@
         <v>-0.5846</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.8905</v>
+        <v>-0.9065</v>
       </c>
       <c r="E100" t="n">
         <v>-1.1612</v>
@@ -5050,25 +5050,25 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-1.2945</v>
+        <v>-1.2658</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6373</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.9443</v>
+        <v>-0.9482</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.2945</v>
+        <v>-1.2658</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.2945</v>
+        <v>-1.2658</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>-1.2945</v>
+        <v>-1.2658</v>
       </c>
       <c r="I101" t="n">
         <v>-1.3311</v>
@@ -5096,25 +5096,25 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-1.337</v>
+        <v>-1.332</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.6731</v>
+        <v>-0.6706</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.9615</v>
+        <v>-0.9746</v>
       </c>
       <c r="E102" t="n">
-        <v>-1.337</v>
+        <v>-1.332</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.337</v>
+        <v>-1.332</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.337</v>
+        <v>-1.332</v>
       </c>
       <c r="I102" t="n">
         <v>-1.3432</v>
@@ -5148,7 +5148,7 @@
         <v>-0.7235</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.0019</v>
+        <v>-1.0165</v>
       </c>
       <c r="E103" t="n">
         <v>-1.4371</v>
@@ -5194,7 +5194,7 @@
         <v>-0.7501</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.0233</v>
+        <v>-1.0375</v>
       </c>
       <c r="E104" t="n">
         <v>-1.49</v>
@@ -5230,93 +5230,93 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-1.7302</v>
+        <v>-1.71</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.8711</v>
+        <v>-0.8609</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.1203</v>
+        <v>-1.1252</v>
       </c>
       <c r="E105" t="n">
-        <v>-1.7302</v>
+        <v>-1.71</v>
       </c>
       <c r="F105" t="n">
-        <v>-1.7302</v>
+        <v>-1.1096</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>-0.6004</v>
       </c>
       <c r="H105" t="n">
-        <v>-1.7302</v>
+        <v>-1.1096</v>
       </c>
       <c r="I105" t="n">
-        <v>-1.7383</v>
+        <v>-1.1668</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>-0.6004</v>
       </c>
       <c r="K105" t="n">
-        <v>290</v>
+        <v>465</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M105" t="n">
-        <v>-1.7383</v>
+        <v>-1.7672</v>
       </c>
       <c r="N105" t="n">
-        <v>290</v>
+        <v>541</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-1.7351</v>
+        <v>-1.7238</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.8679</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.1223</v>
+        <v>-1.1307</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.7351</v>
+        <v>-1.7238</v>
       </c>
       <c r="F106" t="n">
-        <v>-1.1347</v>
+        <v>-1.7238</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.6004</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.1347</v>
+        <v>-1.7238</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.1668</v>
+        <v>-1.7383</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.6004</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>465</v>
+        <v>290</v>
       </c>
       <c r="L106" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>-1.7672</v>
+        <v>-1.7383</v>
       </c>
       <c r="N106" t="n">
-        <v>541</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107">
@@ -5326,25 +5326,25 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-1.747</v>
+        <v>-1.734</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.873</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.1271</v>
+        <v>-1.1347</v>
       </c>
       <c r="E107" t="n">
-        <v>-1.747</v>
+        <v>-1.734</v>
       </c>
       <c r="F107" t="n">
-        <v>-1.747</v>
+        <v>-1.734</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.747</v>
+        <v>-1.734</v>
       </c>
       <c r="I107" t="n">
         <v>-1.7633</v>
@@ -5378,7 +5378,7 @@
         <v>-0.9708</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.2003</v>
+        <v>-1.2121</v>
       </c>
       <c r="E108" t="n">
         <v>-1.9282</v>
@@ -5424,7 +5424,7 @@
         <v>-1.1095</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.3116</v>
+        <v>-1.3219</v>
       </c>
       <c r="E109" t="n">
         <v>-2.2038</v>
@@ -5470,7 +5470,7 @@
         <v>-1.1492</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.3435</v>
+        <v>-1.3533</v>
       </c>
       <c r="E110" t="n">
         <v>-2.2827</v>
@@ -5516,7 +5516,7 @@
         <v>-1.2097</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.392</v>
+        <v>-1.4012</v>
       </c>
       <c r="E111" t="n">
         <v>-2.4028</v>
@@ -5562,7 +5562,7 @@
         <v>-1.2223</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.4021</v>
+        <v>-1.4111</v>
       </c>
       <c r="E112" t="n">
         <v>-2.4278</v>
@@ -5608,7 +5608,7 @@
         <v>-1.24</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.4164</v>
+        <v>-1.4252</v>
       </c>
       <c r="E113" t="n">
         <v>-2.463</v>
@@ -5654,7 +5654,7 @@
         <v>-1.4778</v>
       </c>
       <c r="D114" t="n">
-        <v>-1.6072</v>
+        <v>-1.6133</v>
       </c>
       <c r="E114" t="n">
         <v>-2.9353</v>
@@ -5700,7 +5700,7 @@
         <v>-1.4908</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.6176</v>
+        <v>-1.6237</v>
       </c>
       <c r="E115" t="n">
         <v>-2.9612</v>
@@ -5746,7 +5746,7 @@
         <v>-1.5162</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.6379</v>
+        <v>-1.6437</v>
       </c>
       <c r="E116" t="n">
         <v>-3.0115</v>
@@ -5792,7 +5792,7 @@
         <v>-1.5519</v>
       </c>
       <c r="D117" t="n">
-        <v>-1.6666</v>
+        <v>-1.672</v>
       </c>
       <c r="E117" t="n">
         <v>-3.0825</v>
@@ -5838,7 +5838,7 @@
         <v>-1.5736</v>
       </c>
       <c r="D118" t="n">
-        <v>-1.6841</v>
+        <v>-1.6892</v>
       </c>
       <c r="E118" t="n">
         <v>-3.1257</v>
@@ -5884,7 +5884,7 @@
         <v>-1.6783</v>
       </c>
       <c r="D119" t="n">
-        <v>-1.7681</v>
+        <v>-1.772</v>
       </c>
       <c r="E119" t="n">
         <v>-3.3336</v>
@@ -5930,7 +5930,7 @@
         <v>-1.7155</v>
       </c>
       <c r="D120" t="n">
-        <v>-1.7979</v>
+        <v>-1.8014</v>
       </c>
       <c r="E120" t="n">
         <v>-3.4074</v>
@@ -5976,7 +5976,7 @@
         <v>-1.7426</v>
       </c>
       <c r="D121" t="n">
-        <v>-1.8196</v>
+        <v>-1.8229</v>
       </c>
       <c r="E121" t="n">
         <v>-3.4612</v>
@@ -6016,25 +6016,25 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-3.691</v>
+        <v>-3.6432</v>
       </c>
       <c r="C122" t="n">
-        <v>-1.8582</v>
+        <v>-1.8342</v>
       </c>
       <c r="D122" t="n">
-        <v>-1.9124</v>
+        <v>-1.8954</v>
       </c>
       <c r="E122" t="n">
-        <v>-3.691</v>
+        <v>-3.6432</v>
       </c>
       <c r="F122" t="n">
-        <v>-2.5831</v>
+        <v>-2.5353</v>
       </c>
       <c r="G122" t="n">
         <v>-1.1079</v>
       </c>
       <c r="H122" t="n">
-        <v>-2.5831</v>
+        <v>-2.5353</v>
       </c>
       <c r="I122" t="n">
         <v>-2.6438</v>
@@ -6068,7 +6068,7 @@
         <v>-1.9078</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.9522</v>
+        <v>-1.9536</v>
       </c>
       <c r="E123" t="n">
         <v>-3.7895</v>
@@ -6114,7 +6114,7 @@
         <v>-2.1052</v>
       </c>
       <c r="D124" t="n">
-        <v>-2.1106</v>
+        <v>-2.1099</v>
       </c>
       <c r="E124" t="n">
         <v>-4.1816</v>
